--- a/output/pdf_financials_xlsx/XTD.xlsx
+++ b/output/pdf_financials_xlsx/XTD.xlsx
@@ -2113,40 +2113,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>3.087669</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.325566</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.778204</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.40303</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.101941</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.376395</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.599328</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.486972</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>3.054134</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>5.194324</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.977744</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>8.870628999999999</v>
       </c>
     </row>
     <row r="35">
@@ -2199,40 +2199,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>3.087669</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.325566</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.778204</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.40303</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.101941</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.376395</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2.599328</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.486972</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>3.054134</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>5.194324</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.977744</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>8.870628999999999</v>
       </c>
     </row>
     <row r="37">
@@ -2724,31 +2724,31 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>24.56565</v>
+        <v>22.16262</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>52.772969</v>
+        <v>50.671028</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>47.50398</v>
+        <v>47.127585</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>52.918162</v>
+        <v>50.318834</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>56.563726</v>
+        <v>54.076754</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>54.42476</v>
+        <v>51.370626</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>54.085551</v>
+        <v>48.891227</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>87.06221600000001</v>
+        <v>85.08447200000001</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>89.743973</v>
+        <v>80.873344</v>
       </c>
     </row>
     <row r="49">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">

--- a/output/pdf_financials_xlsx/XTD.xlsx
+++ b/output/pdf_financials_xlsx/XTD.xlsx
@@ -712,40 +712,40 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.152672</v>
+        <v>0.1729</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.15612</v>
+        <v>0.17579</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.155827</v>
+        <v>0.176287</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.156101</v>
+        <v>0.177561</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.265269</v>
+        <v>0.288852</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.336144</v>
+        <v>0.359727</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.336279</v>
+        <v>0.359862</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.368481</v>
+        <v>0.392064</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.408033</v>
+        <v>0.431616</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.377044</v>
+        <v>0.400627</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.527544</v>
+        <v>0.551127</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.607486</v>
+        <v>0.629511</v>
       </c>
     </row>
     <row r="8">
@@ -5760,40 +5760,40 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>5.805013</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>3.022095</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>6.321594</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>3.282632</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>3.0066</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.933236</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>6.009283</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>8.252015999999999</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>3.2406</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>4.653295</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>2.016706</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>6.551935</v>
       </c>
     </row>
     <row r="116">
@@ -6483,40 +6483,26 @@
       <c r="F130" s="3" t="n">
         <v>2.40303</v>
       </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G130" s="3" t="n">
+        <v>2.101941</v>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>0.376395</v>
+      </c>
+      <c r="I130" s="3" t="n">
+        <v>2.599328</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>2.486972</v>
+      </c>
+      <c r="K130" s="3" t="n">
+        <v>3.054134</v>
+      </c>
+      <c r="L130" s="3" t="n">
+        <v>13.369719</v>
+      </c>
+      <c r="M130" s="3" t="n">
+        <v>1.977744</v>
       </c>
     </row>
     <row r="131">
@@ -6626,40 +6612,26 @@
       <c r="F133" s="3" t="n">
         <v>2.101941</v>
       </c>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G133" s="3" t="n">
+        <v>0.376395</v>
+      </c>
+      <c r="H133" s="3" t="n">
+        <v>2.599328</v>
+      </c>
+      <c r="I133" s="3" t="n">
+        <v>2.486972</v>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>3.054134</v>
+      </c>
+      <c r="K133" s="3" t="n">
+        <v>5.194324</v>
+      </c>
+      <c r="L133" s="3" t="n">
+        <v>1.977744</v>
+      </c>
+      <c r="M133" s="3" t="n">
+        <v>8.870628999999999</v>
       </c>
     </row>
     <row r="134">
@@ -11576,7 +11548,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -12328,7 +12304,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -12402,7 +12382,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -13398,7 +13382,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -14030,7 +14018,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -14100,7 +14092,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -15926,7 +15922,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -15998,7 +15998,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -17112,7 +17116,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E145" s="5" t="n">
         <v>5.805013</v>
       </c>
@@ -21666,7 +21674,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -23574,7 +23586,11 @@
           <t>Director’s fees</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -26726,7 +26742,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E279" s="5" t="n">
         <v>0.020228</v>
       </c>
